--- a/report/workbooks/cg_workbook.xlsx
+++ b/report/workbooks/cg_workbook.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Ray_Tracing'!$A$1:$J$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Thermal_Kernels'!$A$1:$Z$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Duty_Cycle'!$A$1:$Z$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Performance'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Performance'!$A$1:$I$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -363,6 +363,155 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Frame time per configuration (ms)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Performance'!B6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Performance'!$A$7:$A$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Performance'!$B$7:$B$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Performance'!C6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Performance'!$A$7:$A$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Performance'!$C$7:$C$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>ms</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3528,7 +3677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3620,54 +3769,382 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>TODO: no bench.csv yet</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EPIC day 10:30</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>14.8698</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <v>17.7085</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>67.2503</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>256.151</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>5725520</v>
+      </c>
+      <c r="G7" s="27">
+        <f>IF(B7&gt;0,1000/B7,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="27">
+        <f>G7-D7</f>
+        <v/>
+      </c>
+      <c r="I7" s="7">
+        <f>IF(E7&gt;0,F7/E7,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>EPIC night 23:00 (game: waves, UAVs)</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>16.3802</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>20.815</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>61.0493</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>970.4299999999999</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>5798500</v>
+      </c>
+      <c r="G8" s="27">
+        <f>IF(B8&gt;0,1000/B8,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="27">
+        <f>G8-D8</f>
+        <v/>
+      </c>
+      <c r="I8" s="7">
+        <f>IF(E8&gt;0,F8/E8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>EPIC day, thermal view</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>10.717</v>
+      </c>
+      <c r="C9" s="24" t="n">
+        <v>14.7982</v>
+      </c>
+      <c r="D9" s="24" t="n">
+        <v>93.30970000000001</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>71.2342</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>2726600</v>
+      </c>
+      <c r="G9" s="27">
+        <f>IF(B9&gt;0,1000/B9,0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="27">
+        <f>G9-D9</f>
+        <v/>
+      </c>
+      <c r="I9" s="7">
+        <f>IF(E9&gt;0,F9/E9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>EPIC night, thermal view</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>12.6203</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>17.6151</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>79.2376</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>66.98399999999999</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>2499130</v>
+      </c>
+      <c r="G10" s="27">
+        <f>IF(B10&gt;0,1000/B10,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="27">
+        <f>G10-D10</f>
+        <v/>
+      </c>
+      <c r="I10" s="7">
+        <f>IF(E10&gt;0,F10/E10,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>EPIC day, shadows off</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>16.4236</v>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>21.0203</v>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>60.8879</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>205.716</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>5857520</v>
+      </c>
+      <c r="G11" s="27">
+        <f>IF(B11&gt;0,1000/B11,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="27">
+        <f>G11-D11</f>
+        <v/>
+      </c>
+      <c r="I11" s="7">
+        <f>IF(E11&gt;0,F11/E11,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>EPIC night, shadows off</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>17.1765</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>22.0255</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>58.2192</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>905.495</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>5867990</v>
+      </c>
+      <c r="G12" s="27">
+        <f>IF(B12&gt;0,1000/B12,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>G12-D12</f>
+        <v/>
+      </c>
+      <c r="I12" s="7">
+        <f>IF(E12&gt;0,F12/E12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>EPIC day, non-indexed</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>54.4709</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>59.4733</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>18.3584</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>4045.85</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>5855790</v>
+      </c>
+      <c r="G13" s="27">
+        <f>IF(B13&gt;0,1000/B13,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="27">
+        <f>G13-D13</f>
+        <v/>
+      </c>
+      <c r="I13" s="7">
+        <f>IF(E13&gt;0,F13/E13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ULTRA day</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>16.7587</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>22.0811</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>59.6704</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>257.236</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>4307730</v>
+      </c>
+      <c r="G14" s="27">
+        <f>IF(B14&gt;0,1000/B14,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="27">
+        <f>G14-D14</f>
+        <v/>
+      </c>
+      <c r="I14" s="7">
+        <f>IF(E14&gt;0,F14/E14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH day</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>15.1059</v>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>17.2516</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>66.1991</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>168.717</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>1411360</v>
+      </c>
+      <c r="G15" s="27">
+        <f>IF(B15&gt;0,1000/B15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="27">
+        <f>G15-D15</f>
+        <v/>
+      </c>
+      <c r="I15" s="7">
+        <f>IF(E15&gt;0,F15/E15,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>LOW day</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>14.1625</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>16.0442</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>70.60899999999999</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>165.434</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>1315170</v>
+      </c>
+      <c r="G16" s="27">
+        <f>IF(B16&gt;0,1000/B16,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="27">
+        <f>G16-D16</f>
+        <v/>
+      </c>
+      <c r="I16" s="7">
+        <f>IF(E16&gt;0,F16/E16,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>v1 look (no post) day</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>13.009</v>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>14.6926</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>1341050</v>
+      </c>
+      <c r="G17" s="27">
+        <f>IF(B17&gt;0,1000/B17,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="27">
+        <f>G17-D17</f>
+        <v/>
+      </c>
+      <c r="I17" s="7">
+        <f>IF(E17&gt;0,F17/E17,0)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <printOptions gridLines="0"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/report/workbooks/cg_workbook.xlsx
+++ b/report/workbooks/cg_workbook.xlsx
@@ -4152,7 +4152,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:T202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -15960,7 +15960,7 @@
   </sheetData>
   <printOptions gridLines="0"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="75"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="41" min="0" max="16383" man="1"/>
     <brk id="124" min="0" max="16383" man="1"/>
@@ -20662,7 +20662,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -22313,7 +22313,7 @@
   </sheetData>
   <printOptions gridLines="0"/>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="78"/>
 </worksheet>
 </file>
 

--- a/report/workbooks/cg_workbook.xlsx
+++ b/report/workbooks/cg_workbook.xlsx
@@ -16,8 +16,11 @@
     <sheet name="Color_Interp" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Ray_Tracing" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Thermal_Kernels" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Duty_Cycle" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Performance" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Tracking" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Line_Follower" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Explosion" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Duty_Cycle" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Performance" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Primitives'!$A$1:$Q$31</definedName>
@@ -29,8 +32,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Color_Interp'!$A$1:$U$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Ray_Tracing'!$A$1:$J$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Thermal_Kernels'!$A$1:$Z$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Duty_Cycle'!$A$1:$Z$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'Performance'!$A$1:$I$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Tracking'!$A$1:$U$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'Line_Follower'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'Explosion'!$A$1:$S$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'Duty_Cycle'!$A$1:$Z$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'Performance'!$A$1:$I$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,9 +44,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -166,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -220,6 +227,7 @@
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1792,6 +1800,3432 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:U42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tracking: Kalman predict / gate / update, two-view triangulation, time on target</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Legend: yellow = input from the code; white = formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source: vision/MultiTracker.cpp predict, mahalanobis2, kalmanUpdate, triangulate; ai/Squad.cpp roundFlightTime, planStrike. Worked example values in yellow; q, gate, flight model from --export-docs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>A. Predict: x' = F x, P' = F P F^T + Q (white-noise acceleration q)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>dt (s)</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>q (m/s2)</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>gate</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>meas. sigma (m)</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>x = (x, z, vx, vz)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>P (before)</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>F P</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="15">
+        <f>$D$6^2*$B$6^4/4</f>
+        <v/>
+      </c>
+      <c r="N9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="15">
+        <f>$D$6^2*$B$6^3/2</f>
+        <v/>
+      </c>
+      <c r="P9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="15">
+        <f>C9*H9+D9*H10+E9*H11+F9*H12</f>
+        <v/>
+      </c>
+      <c r="S9" s="15">
+        <f>C9*I9+D9*I10+E9*I11+F9*I12</f>
+        <v/>
+      </c>
+      <c r="T9" s="15">
+        <f>C9*J9+D9*J10+E9*J11+F9*J12</f>
+        <v/>
+      </c>
+      <c r="U9" s="15">
+        <f>C9*K9+D9*K10+E9*K11+F9*K12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="15">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="15">
+        <f>$D$6^2*$B$6^4/4</f>
+        <v/>
+      </c>
+      <c r="O10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="15">
+        <f>$D$6^2*$B$6^3/2</f>
+        <v/>
+      </c>
+      <c r="R10" s="15">
+        <f>C10*H9+D10*H10+E10*H11+F10*H12</f>
+        <v/>
+      </c>
+      <c r="S10" s="15">
+        <f>C10*I9+D10*I10+E10*I11+F10*I12</f>
+        <v/>
+      </c>
+      <c r="T10" s="15">
+        <f>C10*J9+D10*J10+E10*J11+F10*J12</f>
+        <v/>
+      </c>
+      <c r="U10" s="15">
+        <f>C10*K9+D10*K10+E10*K11+F10*K12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="15">
+        <f>$D$6^2*$B$6^3/2</f>
+        <v/>
+      </c>
+      <c r="N11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="15">
+        <f>$D$6^2*$B$6^2</f>
+        <v/>
+      </c>
+      <c r="P11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="15">
+        <f>C11*H9+D11*H10+E11*H11+F11*H12</f>
+        <v/>
+      </c>
+      <c r="S11" s="15">
+        <f>C11*I9+D11*I10+E11*I11+F11*I12</f>
+        <v/>
+      </c>
+      <c r="T11" s="15">
+        <f>C11*J9+D11*J10+E11*J11+F11*J12</f>
+        <v/>
+      </c>
+      <c r="U11" s="15">
+        <f>C11*K9+D11*K10+E11*K11+F11*K12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="15">
+        <f>$D$6^2*$B$6^3/2</f>
+        <v/>
+      </c>
+      <c r="O12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="15">
+        <f>$D$6^2*$B$6^2</f>
+        <v/>
+      </c>
+      <c r="R12" s="15">
+        <f>C12*H9+D12*H10+E12*H11+F12*H12</f>
+        <v/>
+      </c>
+      <c r="S12" s="15">
+        <f>C12*I9+D12*I10+E12*I11+F12*I12</f>
+        <v/>
+      </c>
+      <c r="T12" s="15">
+        <f>C12*J9+D12*J10+E12*J11+F12*J12</f>
+        <v/>
+      </c>
+      <c r="U12" s="15">
+        <f>C12*K9+D12*K10+E12*K11+F12*K12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>x' = F x</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>P' = F P F^T + Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15">
+        <f>C9*$A$9+D9*$A$10+E9*$A$11+F9*$A$12</f>
+        <v/>
+      </c>
+      <c r="C15" s="15">
+        <f>R9*C9+S9*D9+T9*E9+U9*F9+M9</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>R9*C10+S9*D10+T9*E10+U9*F10+N9</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>R9*C11+S9*D11+T9*E11+U9*F11+O9</f>
+        <v/>
+      </c>
+      <c r="F15" s="15">
+        <f>R9*C12+S9*D12+T9*E12+U9*F12+P9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15">
+        <f>C10*$A$9+D10*$A$10+E10*$A$11+F10*$A$12</f>
+        <v/>
+      </c>
+      <c r="C16" s="15">
+        <f>R10*C9+S10*D9+T10*E9+U10*F9+M10</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>R10*C10+S10*D10+T10*E10+U10*F10+N10</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
+        <f>R10*C11+S10*D11+T10*E11+U10*F11+O10</f>
+        <v/>
+      </c>
+      <c r="F16" s="15">
+        <f>R10*C12+S10*D12+T10*E12+U10*F12+P10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15">
+        <f>C11*$A$9+D11*$A$10+E11*$A$11+F11*$A$12</f>
+        <v/>
+      </c>
+      <c r="C17" s="15">
+        <f>R11*C9+S11*D9+T11*E9+U11*F9+M11</f>
+        <v/>
+      </c>
+      <c r="D17" s="15">
+        <f>R11*C10+S11*D10+T11*E10+U11*F10+N11</f>
+        <v/>
+      </c>
+      <c r="E17" s="15">
+        <f>R11*C11+S11*D11+T11*E11+U11*F11+O11</f>
+        <v/>
+      </c>
+      <c r="F17" s="15">
+        <f>R11*C12+S11*D12+T11*E12+U11*F12+P11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15">
+        <f>C12*$A$9+D12*$A$10+E12*$A$11+F12*$A$12</f>
+        <v/>
+      </c>
+      <c r="C18" s="15">
+        <f>R12*C9+S12*D9+T12*E9+U12*F9+M12</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>R12*C10+S12*D10+T12*E10+U12*F10+N12</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>R12*C11+S12*D11+T12*E11+U12*F11+O12</f>
+        <v/>
+      </c>
+      <c r="F18" s="15">
+        <f>R12*C12+S12*D12+T12*E12+U12*F12+P12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>B. Gate and update with a measurement m (ground point)</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>D. Time on target (roundFlightTime, planStrike)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>m = (x, z)</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>accel</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>ramp (s)</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>cruise</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>fuse (m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>innovation nu</t>
+        </is>
+      </c>
+      <c r="B22" s="19">
+        <f>B21-A15</f>
+        <v/>
+      </c>
+      <c r="C22" s="19">
+        <f>C21-A16</f>
+        <v/>
+      </c>
+      <c r="M22" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="N22" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="O22" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P22" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q22" s="24" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>S = H P' H^T + sigma^2 I</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>S^-1</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>K = P' H^T S^-1 (4x2)</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>x_new = x' + K nu</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>UAV</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>distance</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>d - fuse</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>ramp dist</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>T (s)</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>launch +s</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15">
+        <f>C15+$I$6^2</f>
+        <v/>
+      </c>
+      <c r="B24" s="15">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="D24" s="15">
+        <f>B25/(A24*B25-B24*A25)</f>
+        <v/>
+      </c>
+      <c r="E24" s="15">
+        <f>-B24/(A24*B25-B24*A25)</f>
+        <v/>
+      </c>
+      <c r="G24" s="15">
+        <f>C15*D24+D15*D25</f>
+        <v/>
+      </c>
+      <c r="H24" s="15">
+        <f>C15*E24+D15*E25</f>
+        <v/>
+      </c>
+      <c r="J24" s="15">
+        <f>A15+G24*B22+H24*C22</f>
+        <v/>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="O24" s="19">
+        <f>MAX(0,N24-$Q$22)</f>
+        <v/>
+      </c>
+      <c r="P24" s="19">
+        <f>0.5*($M$22+$P$22)*$O$22</f>
+        <v/>
+      </c>
+      <c r="Q24" s="19">
+        <f>IF(O24&lt;=P24,(-$M$22+SQRT($M$22^2+2*$N$22*O24))/$N$22,$O$22+(O24-P24)/$P$22)</f>
+        <v/>
+      </c>
+      <c r="R24" s="19">
+        <f>MAX(Q24,Q25)-Q24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15">
+        <f>C16</f>
+        <v/>
+      </c>
+      <c r="B25" s="15">
+        <f>D16+$I$6^2</f>
+        <v/>
+      </c>
+      <c r="D25" s="15">
+        <f>-A25/(A24*B25-B24*A25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="15">
+        <f>A24/(A24*B25-B24*A25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="15">
+        <f>C16*D24+D16*D25</f>
+        <v/>
+      </c>
+      <c r="H25" s="15">
+        <f>C16*E24+D16*E25</f>
+        <v/>
+      </c>
+      <c r="J25" s="15">
+        <f>A16+G25*B22+H25*C22</f>
+        <v/>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="O25" s="19">
+        <f>MAX(0,N25-$Q$22)</f>
+        <v/>
+      </c>
+      <c r="P25" s="19">
+        <f>0.5*($M$22+$P$22)*$O$22</f>
+        <v/>
+      </c>
+      <c r="Q25" s="19">
+        <f>IF(O25&lt;=P25,(-$M$22+SQRT($M$22^2+2*$N$22*O25))/$N$22,$O$22+(O25-P25)/$P$22)</f>
+        <v/>
+      </c>
+      <c r="R25" s="19">
+        <f>MAX(Q24,Q25)-Q25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="G26" s="15">
+        <f>C17*D24+D17*D25</f>
+        <v/>
+      </c>
+      <c r="H26" s="15">
+        <f>C17*E24+D17*E25</f>
+        <v/>
+      </c>
+      <c r="J26" s="15">
+        <f>A17+G26*B22+H26*C22</f>
+        <v/>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>both rounds arrive together: launch delay = T_far - T_k</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>d^2 = nu^T S^-1 nu</t>
+        </is>
+      </c>
+      <c r="C27" s="19">
+        <f>B22*(D24*B22+E24*C22)+C22*(D25*B22+E25*C22)</f>
+        <v/>
+      </c>
+      <c r="D27" s="15">
+        <f>IF(C27&lt;$F$6,"inside gate","rejected")</f>
+        <v/>
+      </c>
+      <c r="G27" s="15">
+        <f>C18*D24+D18*D25</f>
+        <v/>
+      </c>
+      <c r="H27" s="15">
+        <f>C18*E24+D18*E25</f>
+        <v/>
+      </c>
+      <c r="J27" s="15">
+        <f>A18+G27*B22+H27*C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>C. Two-view triangulation: minimise |o1 + s d1 - (o2 + t d2)|</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="3" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>o1 (UAV 1)</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="n">
+        <v>-6</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>d1</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D33" s="24" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>o2 (UAV 2)</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" s="24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>d2</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C35" s="24" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="D35" s="24" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>a = d1.d1</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>($B$33*$B$33+$C$33*$C$33+$D$33*$D$33)</f>
+        <v/>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>b = d1.d2</t>
+        </is>
+      </c>
+      <c r="D36" s="19">
+        <f>($B$33*$B$35+$C$33*$C$35+$D$33*$D$35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>c = d2.d2</t>
+        </is>
+      </c>
+      <c r="F36" s="19">
+        <f>($B$35*$B$35+$C$35*$C$35+$D$35*$D$35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>d = d1.w</t>
+        </is>
+      </c>
+      <c r="H36" s="19">
+        <f>($B$33*($B$32-$B$34)+$C$33*($C$32-$C$34)+$D$33*($D$32-$D$34))</f>
+        <v/>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>e = d2.w</t>
+        </is>
+      </c>
+      <c r="J36" s="19">
+        <f>($B$35*($B$32-$B$34)+$C$35*($C$32-$C$34)+$D$35*($D$32-$D$34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>($D$36*$J$36-$F$36*$H$36)/($B$36*$F$36-$D$36^2)</f>
+        <v/>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D37" s="19">
+        <f>($B$36*$J$36-$D$36*$H$36)/($B$36*$F$36-$D$36^2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr"/>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>p1 = o1 + s d1</t>
+        </is>
+      </c>
+      <c r="B39" s="19">
+        <f>$B$32+$B$37*$B$33</f>
+        <v/>
+      </c>
+      <c r="C39" s="19">
+        <f>$C$32+$B$37*$C$33</f>
+        <v/>
+      </c>
+      <c r="D39" s="19">
+        <f>$D$32+$B$37*$D$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>p2 = o2 + t d2</t>
+        </is>
+      </c>
+      <c r="B40" s="19">
+        <f>$B$34+$D$37*$B$35</f>
+        <v/>
+      </c>
+      <c r="C40" s="19">
+        <f>$C$34+$D$37*$C$35</f>
+        <v/>
+      </c>
+      <c r="D40" s="19">
+        <f>$D$34+$D$37*$D$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>midpoint</t>
+        </is>
+      </c>
+      <c r="B41" s="19">
+        <f>(B39+B40)/2</f>
+        <v/>
+      </c>
+      <c r="C41" s="19">
+        <f>(C39+C40)/2</f>
+        <v/>
+      </c>
+      <c r="D41" s="19">
+        <f>(D39+D40)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>residual |p1-p2|</t>
+        </is>
+      </c>
+      <c r="B42" s="19">
+        <f>SQRT((B39-B40)^2+(C39-C40)^2+(D39-D40)^2)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G6:H6"/>
+  </mergeCells>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line_Follower: IR sensor array, PD steering, differential drive (one tick)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Legend: yellow = input from the code; white = formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source: ai/HideController.cpp followLine (kSensorForward, kSensorSpacing, kLineHalfWidth, kKp, kKd, kMaxSpeed); objects/Rover.h kRoverTrackWidth. Line offset, previous error and dt are worked-example inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>spacing (m)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>half width</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>err scale</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Kp</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Kd</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>v max</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>slow-down</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>omega max</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>track w</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>line offset</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>prev e</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>dt (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>inputs</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L6" s="31" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M6" s="31" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>A. Sensors: lateral offset x_i = -2 spacing + i spacing (left &gt; 0); on the line if |x_i - line| &lt; half width</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>sensor i</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>x_i (m)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>|x_i - line|</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>on line</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" s="19">
+        <f>-2*$B$6+A10*$B$6</f>
+        <v/>
+      </c>
+      <c r="C10" s="19">
+        <f>ABS(B10-$K$6)</f>
+        <v/>
+      </c>
+      <c r="D10" s="7">
+        <f>IF(C10&lt;$C$6,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="19">
+        <f>-2*$B$6+A11*$B$6</f>
+        <v/>
+      </c>
+      <c r="C11" s="19">
+        <f>ABS(B11-$K$6)</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>IF(C11&lt;$C$6,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="19">
+        <f>-2*$B$6+A12*$B$6</f>
+        <v/>
+      </c>
+      <c r="C12" s="19">
+        <f>ABS(B12-$K$6)</f>
+        <v/>
+      </c>
+      <c r="D12" s="7">
+        <f>IF(C12&lt;$C$6,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="19">
+        <f>-2*$B$6+A13*$B$6</f>
+        <v/>
+      </c>
+      <c r="C13" s="19">
+        <f>ABS(B13-$K$6)</f>
+        <v/>
+      </c>
+      <c r="D13" s="7">
+        <f>IF(C13&lt;$C$6,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="19">
+        <f>-2*$B$6+A14*$B$6</f>
+        <v/>
+      </c>
+      <c r="C14" s="19">
+        <f>ABS(B14-$K$6)</f>
+        <v/>
+      </c>
+      <c r="D14" s="7">
+        <f>IF(C14&lt;$C$6,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>B. PD steering and wheel speeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>active sensors</t>
+        </is>
+      </c>
+      <c r="B17" s="19">
+        <f>SUM(D10:D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>error e</t>
+        </is>
+      </c>
+      <c r="B18" s="19">
+        <f>IF(B17&gt;0,SUMPRODUCT(B10:B14,D10:D14)/B17/$D$6,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>de/dt</t>
+        </is>
+      </c>
+      <c r="B19" s="19">
+        <f>(B18-$L$6)/$M$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>omega (rad/s)</t>
+        </is>
+      </c>
+      <c r="B20" s="19">
+        <f>MAX(-$I$6,MIN($I$6,$E$6*B18+$F$6*B19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>speed v (m/s)</t>
+        </is>
+      </c>
+      <c r="B21" s="19">
+        <f>$G$6*(1-$H$6*ABS(B18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>left wheel</t>
+        </is>
+      </c>
+      <c r="B22" s="19">
+        <f>B21-B20*$J$6/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>right wheel</t>
+        </is>
+      </c>
+      <c r="B23" s="19">
+        <f>B21+B20*$J$6/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>turn</t>
+        </is>
+      </c>
+      <c r="B24" s="15">
+        <f>IF(B20&gt;0,"left",IF(B20&lt;0,"right","straight"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Rate limits (kWheelAccel) and the line-lost search are not modelled here; see followLine.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:S56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Explosion: colour from temperature, particle motion, debris bounce</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Legend: yellow = input from the code; white = formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source: rendering/Effects.cpp bb(T), fire / spark colour; scene/Combat.cpp updateParticles (spark integrator); scene/Scene.cpp updateDebris (restitution). Yellow = constants copied from the code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>bb R exp</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>bb G exp</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>bb B gain</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>bb B exp</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>fire life exp</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>emit a</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>emit b</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>spark cool</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="24" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>A. Blackbody ramp bb(T) = (T^a, T^b, k T^c) and fire emission bb(T)(a' + b' T^2)</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>B. A flame core and a spark over their lives (t = age / life)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>a'+b'T^2</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>R emit</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>G emit</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>B emit</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>fire T</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>spark Tn</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>bb arg</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" s="19">
+        <f>A11^$B$7</f>
+        <v/>
+      </c>
+      <c r="C11" s="19">
+        <f>A11^$C$7</f>
+        <v/>
+      </c>
+      <c r="D11" s="19">
+        <f>$D$7*A11^$E$7</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f>$G$7+$H$7*A11^2</f>
+        <v/>
+      </c>
+      <c r="F11" s="19">
+        <f>B11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="19">
+        <f>C11*E11</f>
+        <v/>
+      </c>
+      <c r="H11" s="19">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="19">
+        <f>(1-J11)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L11" s="19">
+        <f>K11^$B$7</f>
+        <v/>
+      </c>
+      <c r="M11" s="19">
+        <f>K11^$C$7</f>
+        <v/>
+      </c>
+      <c r="N11" s="19">
+        <f>$D$7*K11^$E$7</f>
+        <v/>
+      </c>
+      <c r="O11" s="19">
+        <f>MAX(0,MIN(1,1-J11*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P11" s="19">
+        <f>0.1+0.9*O11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="19">
+        <f>P11^$B$7</f>
+        <v/>
+      </c>
+      <c r="R11" s="19">
+        <f>P11^$C$7</f>
+        <v/>
+      </c>
+      <c r="S11" s="19">
+        <f>$D$7*P11^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B12" s="19">
+        <f>A12^$B$7</f>
+        <v/>
+      </c>
+      <c r="C12" s="19">
+        <f>A12^$C$7</f>
+        <v/>
+      </c>
+      <c r="D12" s="19">
+        <f>$D$7*A12^$E$7</f>
+        <v/>
+      </c>
+      <c r="E12" s="19">
+        <f>$G$7+$H$7*A12^2</f>
+        <v/>
+      </c>
+      <c r="F12" s="19">
+        <f>B12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="19">
+        <f>C12*E12</f>
+        <v/>
+      </c>
+      <c r="H12" s="19">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="J12" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K12" s="19">
+        <f>(1-J12)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L12" s="19">
+        <f>K12^$B$7</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
+        <f>K12^$C$7</f>
+        <v/>
+      </c>
+      <c r="N12" s="19">
+        <f>$D$7*K12^$E$7</f>
+        <v/>
+      </c>
+      <c r="O12" s="19">
+        <f>MAX(0,MIN(1,1-J12*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P12" s="19">
+        <f>0.1+0.9*O12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="19">
+        <f>P12^$B$7</f>
+        <v/>
+      </c>
+      <c r="R12" s="19">
+        <f>P12^$C$7</f>
+        <v/>
+      </c>
+      <c r="S12" s="19">
+        <f>$D$7*P12^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B13" s="19">
+        <f>A13^$B$7</f>
+        <v/>
+      </c>
+      <c r="C13" s="19">
+        <f>A13^$C$7</f>
+        <v/>
+      </c>
+      <c r="D13" s="19">
+        <f>$D$7*A13^$E$7</f>
+        <v/>
+      </c>
+      <c r="E13" s="19">
+        <f>$G$7+$H$7*A13^2</f>
+        <v/>
+      </c>
+      <c r="F13" s="19">
+        <f>B13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="19">
+        <f>C13*E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="19">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="J13" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K13" s="19">
+        <f>(1-J13)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L13" s="19">
+        <f>K13^$B$7</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
+        <f>K13^$C$7</f>
+        <v/>
+      </c>
+      <c r="N13" s="19">
+        <f>$D$7*K13^$E$7</f>
+        <v/>
+      </c>
+      <c r="O13" s="19">
+        <f>MAX(0,MIN(1,1-J13*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P13" s="19">
+        <f>0.1+0.9*O13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="19">
+        <f>P13^$B$7</f>
+        <v/>
+      </c>
+      <c r="R13" s="19">
+        <f>P13^$C$7</f>
+        <v/>
+      </c>
+      <c r="S13" s="19">
+        <f>$D$7*P13^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B14" s="19">
+        <f>A14^$B$7</f>
+        <v/>
+      </c>
+      <c r="C14" s="19">
+        <f>A14^$C$7</f>
+        <v/>
+      </c>
+      <c r="D14" s="19">
+        <f>$D$7*A14^$E$7</f>
+        <v/>
+      </c>
+      <c r="E14" s="19">
+        <f>$G$7+$H$7*A14^2</f>
+        <v/>
+      </c>
+      <c r="F14" s="19">
+        <f>B14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="19">
+        <f>C14*E14</f>
+        <v/>
+      </c>
+      <c r="H14" s="19">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K14" s="19">
+        <f>(1-J14)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L14" s="19">
+        <f>K14^$B$7</f>
+        <v/>
+      </c>
+      <c r="M14" s="19">
+        <f>K14^$C$7</f>
+        <v/>
+      </c>
+      <c r="N14" s="19">
+        <f>$D$7*K14^$E$7</f>
+        <v/>
+      </c>
+      <c r="O14" s="19">
+        <f>MAX(0,MIN(1,1-J14*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P14" s="19">
+        <f>0.1+0.9*O14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="19">
+        <f>P14^$B$7</f>
+        <v/>
+      </c>
+      <c r="R14" s="19">
+        <f>P14^$C$7</f>
+        <v/>
+      </c>
+      <c r="S14" s="19">
+        <f>$D$7*P14^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B15" s="19">
+        <f>A15^$B$7</f>
+        <v/>
+      </c>
+      <c r="C15" s="19">
+        <f>A15^$C$7</f>
+        <v/>
+      </c>
+      <c r="D15" s="19">
+        <f>$D$7*A15^$E$7</f>
+        <v/>
+      </c>
+      <c r="E15" s="19">
+        <f>$G$7+$H$7*A15^2</f>
+        <v/>
+      </c>
+      <c r="F15" s="19">
+        <f>B15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="19">
+        <f>C15*E15</f>
+        <v/>
+      </c>
+      <c r="H15" s="19">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="J15" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K15" s="19">
+        <f>(1-J15)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L15" s="19">
+        <f>K15^$B$7</f>
+        <v/>
+      </c>
+      <c r="M15" s="19">
+        <f>K15^$C$7</f>
+        <v/>
+      </c>
+      <c r="N15" s="19">
+        <f>$D$7*K15^$E$7</f>
+        <v/>
+      </c>
+      <c r="O15" s="19">
+        <f>MAX(0,MIN(1,1-J15*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P15" s="19">
+        <f>0.1+0.9*O15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="19">
+        <f>P15^$B$7</f>
+        <v/>
+      </c>
+      <c r="R15" s="19">
+        <f>P15^$C$7</f>
+        <v/>
+      </c>
+      <c r="S15" s="19">
+        <f>$D$7*P15^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B16" s="19">
+        <f>A16^$B$7</f>
+        <v/>
+      </c>
+      <c r="C16" s="19">
+        <f>A16^$C$7</f>
+        <v/>
+      </c>
+      <c r="D16" s="19">
+        <f>$D$7*A16^$E$7</f>
+        <v/>
+      </c>
+      <c r="E16" s="19">
+        <f>$G$7+$H$7*A16^2</f>
+        <v/>
+      </c>
+      <c r="F16" s="19">
+        <f>B16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="19">
+        <f>C16*E16</f>
+        <v/>
+      </c>
+      <c r="H16" s="19">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="J16" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="19">
+        <f>(1-J16)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L16" s="19">
+        <f>K16^$B$7</f>
+        <v/>
+      </c>
+      <c r="M16" s="19">
+        <f>K16^$C$7</f>
+        <v/>
+      </c>
+      <c r="N16" s="19">
+        <f>$D$7*K16^$E$7</f>
+        <v/>
+      </c>
+      <c r="O16" s="19">
+        <f>MAX(0,MIN(1,1-J16*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P16" s="19">
+        <f>0.1+0.9*O16</f>
+        <v/>
+      </c>
+      <c r="Q16" s="19">
+        <f>P16^$B$7</f>
+        <v/>
+      </c>
+      <c r="R16" s="19">
+        <f>P16^$C$7</f>
+        <v/>
+      </c>
+      <c r="S16" s="19">
+        <f>$D$7*P16^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B17" s="19">
+        <f>A17^$B$7</f>
+        <v/>
+      </c>
+      <c r="C17" s="19">
+        <f>A17^$C$7</f>
+        <v/>
+      </c>
+      <c r="D17" s="19">
+        <f>$D$7*A17^$E$7</f>
+        <v/>
+      </c>
+      <c r="E17" s="19">
+        <f>$G$7+$H$7*A17^2</f>
+        <v/>
+      </c>
+      <c r="F17" s="19">
+        <f>B17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="19">
+        <f>C17*E17</f>
+        <v/>
+      </c>
+      <c r="H17" s="19">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K17" s="19">
+        <f>(1-J17)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L17" s="19">
+        <f>K17^$B$7</f>
+        <v/>
+      </c>
+      <c r="M17" s="19">
+        <f>K17^$C$7</f>
+        <v/>
+      </c>
+      <c r="N17" s="19">
+        <f>$D$7*K17^$E$7</f>
+        <v/>
+      </c>
+      <c r="O17" s="19">
+        <f>MAX(0,MIN(1,1-J17*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P17" s="19">
+        <f>0.1+0.9*O17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="19">
+        <f>P17^$B$7</f>
+        <v/>
+      </c>
+      <c r="R17" s="19">
+        <f>P17^$C$7</f>
+        <v/>
+      </c>
+      <c r="S17" s="19">
+        <f>$D$7*P17^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B18" s="19">
+        <f>A18^$B$7</f>
+        <v/>
+      </c>
+      <c r="C18" s="19">
+        <f>A18^$C$7</f>
+        <v/>
+      </c>
+      <c r="D18" s="19">
+        <f>$D$7*A18^$E$7</f>
+        <v/>
+      </c>
+      <c r="E18" s="19">
+        <f>$G$7+$H$7*A18^2</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>B18*E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>C18*E18</f>
+        <v/>
+      </c>
+      <c r="H18" s="19">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="J18" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K18" s="19">
+        <f>(1-J18)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L18" s="19">
+        <f>K18^$B$7</f>
+        <v/>
+      </c>
+      <c r="M18" s="19">
+        <f>K18^$C$7</f>
+        <v/>
+      </c>
+      <c r="N18" s="19">
+        <f>$D$7*K18^$E$7</f>
+        <v/>
+      </c>
+      <c r="O18" s="19">
+        <f>MAX(0,MIN(1,1-J18*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P18" s="19">
+        <f>0.1+0.9*O18</f>
+        <v/>
+      </c>
+      <c r="Q18" s="19">
+        <f>P18^$B$7</f>
+        <v/>
+      </c>
+      <c r="R18" s="19">
+        <f>P18^$C$7</f>
+        <v/>
+      </c>
+      <c r="S18" s="19">
+        <f>$D$7*P18^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B19" s="19">
+        <f>A19^$B$7</f>
+        <v/>
+      </c>
+      <c r="C19" s="19">
+        <f>A19^$C$7</f>
+        <v/>
+      </c>
+      <c r="D19" s="19">
+        <f>$D$7*A19^$E$7</f>
+        <v/>
+      </c>
+      <c r="E19" s="19">
+        <f>$G$7+$H$7*A19^2</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>B19*E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="19">
+        <f>C19*E19</f>
+        <v/>
+      </c>
+      <c r="H19" s="19">
+        <f>D19*E19</f>
+        <v/>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K19" s="19">
+        <f>(1-J19)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L19" s="19">
+        <f>K19^$B$7</f>
+        <v/>
+      </c>
+      <c r="M19" s="19">
+        <f>K19^$C$7</f>
+        <v/>
+      </c>
+      <c r="N19" s="19">
+        <f>$D$7*K19^$E$7</f>
+        <v/>
+      </c>
+      <c r="O19" s="19">
+        <f>MAX(0,MIN(1,1-J19*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P19" s="19">
+        <f>0.1+0.9*O19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="19">
+        <f>P19^$B$7</f>
+        <v/>
+      </c>
+      <c r="R19" s="19">
+        <f>P19^$C$7</f>
+        <v/>
+      </c>
+      <c r="S19" s="19">
+        <f>$D$7*P19^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B20" s="19">
+        <f>A20^$B$7</f>
+        <v/>
+      </c>
+      <c r="C20" s="19">
+        <f>A20^$C$7</f>
+        <v/>
+      </c>
+      <c r="D20" s="19">
+        <f>$D$7*A20^$E$7</f>
+        <v/>
+      </c>
+      <c r="E20" s="19">
+        <f>$G$7+$H$7*A20^2</f>
+        <v/>
+      </c>
+      <c r="F20" s="19">
+        <f>B20*E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="19">
+        <f>C20*E20</f>
+        <v/>
+      </c>
+      <c r="H20" s="19">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+      <c r="J20" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K20" s="19">
+        <f>(1-J20)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L20" s="19">
+        <f>K20^$B$7</f>
+        <v/>
+      </c>
+      <c r="M20" s="19">
+        <f>K20^$C$7</f>
+        <v/>
+      </c>
+      <c r="N20" s="19">
+        <f>$D$7*K20^$E$7</f>
+        <v/>
+      </c>
+      <c r="O20" s="19">
+        <f>MAX(0,MIN(1,1-J20*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P20" s="19">
+        <f>0.1+0.9*O20</f>
+        <v/>
+      </c>
+      <c r="Q20" s="19">
+        <f>P20^$B$7</f>
+        <v/>
+      </c>
+      <c r="R20" s="19">
+        <f>P20^$C$7</f>
+        <v/>
+      </c>
+      <c r="S20" s="19">
+        <f>$D$7*P20^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="19">
+        <f>A21^$B$7</f>
+        <v/>
+      </c>
+      <c r="C21" s="19">
+        <f>A21^$C$7</f>
+        <v/>
+      </c>
+      <c r="D21" s="19">
+        <f>$D$7*A21^$E$7</f>
+        <v/>
+      </c>
+      <c r="E21" s="19">
+        <f>$G$7+$H$7*A21^2</f>
+        <v/>
+      </c>
+      <c r="F21" s="19">
+        <f>B21*E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="19">
+        <f>C21*E21</f>
+        <v/>
+      </c>
+      <c r="H21" s="19">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+      <c r="J21" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="19">
+        <f>(1-J21)^$F$7</f>
+        <v/>
+      </c>
+      <c r="L21" s="19">
+        <f>K21^$B$7</f>
+        <v/>
+      </c>
+      <c r="M21" s="19">
+        <f>K21^$C$7</f>
+        <v/>
+      </c>
+      <c r="N21" s="19">
+        <f>$D$7*K21^$E$7</f>
+        <v/>
+      </c>
+      <c r="O21" s="19">
+        <f>MAX(0,MIN(1,1-J21*$I$7))</f>
+        <v/>
+      </c>
+      <c r="P21" s="19">
+        <f>0.1+0.9*O21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="19">
+        <f>P21^$B$7</f>
+        <v/>
+      </c>
+      <c r="R21" s="19">
+        <f>P21^$C$7</f>
+        <v/>
+      </c>
+      <c r="S21" s="19">
+        <f>$D$7*P21^$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>C. One spark, step by step: v_y -= g dt; v *= exp(-k dt); p += v dt; below ground: v_y = -e v_y, v_x *= f</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>D. Debris bounces (restitution e, no drag): apex = v^2 / 2g, flight = 2v / g</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>drag k</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>bounce e</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>keep f</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>dt (s)</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>v_x0</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>v_y0</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>y0</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>v0 (m/s)</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>rest below</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>inputs</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D26" s="24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F26" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G26" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K26" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" s="24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M26" s="24" t="n">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>t (s)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>v_x</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>v_y</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>bounce n</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>v_n (m/s)</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>apex (m)</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>flight (s)</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>moving?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="19">
+        <f>$I$26</f>
+        <v/>
+      </c>
+      <c r="E28" s="19">
+        <f>$G$26</f>
+        <v/>
+      </c>
+      <c r="F28" s="19">
+        <f>$H$26</f>
+        <v/>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="19">
+        <f>$K$26*$J$26^J28</f>
+        <v/>
+      </c>
+      <c r="L28" s="19">
+        <f>K28^2/(2*$M$26)</f>
+        <v/>
+      </c>
+      <c r="M28" s="19">
+        <f>2*K28/$M$26</f>
+        <v/>
+      </c>
+      <c r="N28" s="15">
+        <f>IF(K28&gt;=$L$26,"yes","rest")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="19">
+        <f>B28+$F$26</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>C28+E28*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D29" s="19">
+        <f>MAX(0.02,(D28+(F28-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E29" s="19">
+        <f>IF((D28+(F28-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E28*EXP(-$C$26*$F$26)*$E$26,E28*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F29" s="19">
+        <f>IF((D28+(F28-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F28-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F28-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="19">
+        <f>$K$26*$J$26^J29</f>
+        <v/>
+      </c>
+      <c r="L29" s="19">
+        <f>K29^2/(2*$M$26)</f>
+        <v/>
+      </c>
+      <c r="M29" s="19">
+        <f>2*K29/$M$26</f>
+        <v/>
+      </c>
+      <c r="N29" s="15">
+        <f>IF(K29&gt;=$L$26,"yes","rest")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="19">
+        <f>B29+$F$26</f>
+        <v/>
+      </c>
+      <c r="C30" s="19">
+        <f>C29+E29*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D30" s="19">
+        <f>MAX(0.02,(D29+(F29-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E30" s="19">
+        <f>IF((D29+(F29-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E29*EXP(-$C$26*$F$26)*$E$26,E29*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F30" s="19">
+        <f>IF((D29+(F29-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F29-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F29-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="19">
+        <f>$K$26*$J$26^J30</f>
+        <v/>
+      </c>
+      <c r="L30" s="19">
+        <f>K30^2/(2*$M$26)</f>
+        <v/>
+      </c>
+      <c r="M30" s="19">
+        <f>2*K30/$M$26</f>
+        <v/>
+      </c>
+      <c r="N30" s="15">
+        <f>IF(K30&gt;=$L$26,"yes","rest")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="19">
+        <f>B30+$F$26</f>
+        <v/>
+      </c>
+      <c r="C31" s="19">
+        <f>C30+E30*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D31" s="19">
+        <f>MAX(0.02,(D30+(F30-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E31" s="19">
+        <f>IF((D30+(F30-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E30*EXP(-$C$26*$F$26)*$E$26,E30*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F31" s="19">
+        <f>IF((D30+(F30-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F30-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F30-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="19">
+        <f>$K$26*$J$26^J31</f>
+        <v/>
+      </c>
+      <c r="L31" s="19">
+        <f>K31^2/(2*$M$26)</f>
+        <v/>
+      </c>
+      <c r="M31" s="19">
+        <f>2*K31/$M$26</f>
+        <v/>
+      </c>
+      <c r="N31" s="15">
+        <f>IF(K31&gt;=$L$26,"yes","rest")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="19">
+        <f>B31+$F$26</f>
+        <v/>
+      </c>
+      <c r="C32" s="19">
+        <f>C31+E31*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D32" s="19">
+        <f>MAX(0.02,(D31+(F31-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E32" s="19">
+        <f>IF((D31+(F31-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E31*EXP(-$C$26*$F$26)*$E$26,E31*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F32" s="19">
+        <f>IF((D31+(F31-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F31-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F31-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="19">
+        <f>$K$26*$J$26^J32</f>
+        <v/>
+      </c>
+      <c r="L32" s="19">
+        <f>K32^2/(2*$M$26)</f>
+        <v/>
+      </c>
+      <c r="M32" s="19">
+        <f>2*K32/$M$26</f>
+        <v/>
+      </c>
+      <c r="N32" s="15">
+        <f>IF(K32&gt;=$L$26,"yes","rest")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="19">
+        <f>B32+$F$26</f>
+        <v/>
+      </c>
+      <c r="C33" s="19">
+        <f>C32+E32*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D33" s="19">
+        <f>MAX(0.02,(D32+(F32-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E33" s="19">
+        <f>IF((D32+(F32-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E32*EXP(-$C$26*$F$26)*$E$26,E32*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F33" s="19">
+        <f>IF((D32+(F32-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F32-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F32-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="19">
+        <f>$K$26*$J$26^J33</f>
+        <v/>
+      </c>
+      <c r="L33" s="19">
+        <f>K33^2/(2*$M$26)</f>
+        <v/>
+      </c>
+      <c r="M33" s="19">
+        <f>2*K33/$M$26</f>
+        <v/>
+      </c>
+      <c r="N33" s="15">
+        <f>IF(K33&gt;=$L$26,"yes","rest")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="19">
+        <f>B33+$F$26</f>
+        <v/>
+      </c>
+      <c r="C34" s="19">
+        <f>C33+E33*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f>MAX(0.02,(D33+(F33-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E34" s="19">
+        <f>IF((D33+(F33-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E33*EXP(-$C$26*$F$26)*$E$26,E33*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F34" s="19">
+        <f>IF((D33+(F33-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F33-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F33-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="19">
+        <f>B34+$F$26</f>
+        <v/>
+      </c>
+      <c r="C35" s="19">
+        <f>C34+E34*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D35" s="19">
+        <f>MAX(0.02,(D34+(F34-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E35" s="19">
+        <f>IF((D34+(F34-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E34*EXP(-$C$26*$F$26)*$E$26,E34*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
+        <f>IF((D34+(F34-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F34-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F34-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>total time</t>
+        </is>
+      </c>
+      <c r="M35" s="19">
+        <f>SUMIF(N28:N33,"yes",M28:M33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" s="19">
+        <f>B35+$F$26</f>
+        <v/>
+      </c>
+      <c r="C36" s="19">
+        <f>C35+E35*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>MAX(0.02,(D35+(F35-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E36" s="19">
+        <f>IF((D35+(F35-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E35*EXP(-$C$26*$F$26)*$E$26,E35*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
+        <f>IF((D35+(F35-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F35-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F35-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" s="19">
+        <f>B36+$F$26</f>
+        <v/>
+      </c>
+      <c r="C37" s="19">
+        <f>C36+E36*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D37" s="19">
+        <f>MAX(0.02,(D36+(F36-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E37" s="19">
+        <f>IF((D36+(F36-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E36*EXP(-$C$26*$F$26)*$E$26,E36*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F37" s="19">
+        <f>IF((D36+(F36-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F36-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F36-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B38" s="19">
+        <f>B37+$F$26</f>
+        <v/>
+      </c>
+      <c r="C38" s="19">
+        <f>C37+E37*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D38" s="19">
+        <f>MAX(0.02,(D37+(F37-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E38" s="19">
+        <f>IF((D37+(F37-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E37*EXP(-$C$26*$F$26)*$E$26,E37*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F38" s="19">
+        <f>IF((D37+(F37-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F37-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F37-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" s="19">
+        <f>B38+$F$26</f>
+        <v/>
+      </c>
+      <c r="C39" s="19">
+        <f>C38+E38*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D39" s="19">
+        <f>MAX(0.02,(D38+(F38-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E39" s="19">
+        <f>IF((D38+(F38-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E38*EXP(-$C$26*$F$26)*$E$26,E38*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F39" s="19">
+        <f>IF((D38+(F38-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F38-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F38-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B40" s="19">
+        <f>B39+$F$26</f>
+        <v/>
+      </c>
+      <c r="C40" s="19">
+        <f>C39+E39*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D40" s="19">
+        <f>MAX(0.02,(D39+(F39-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E40" s="19">
+        <f>IF((D39+(F39-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E39*EXP(-$C$26*$F$26)*$E$26,E39*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F40" s="19">
+        <f>IF((D39+(F39-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F39-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F39-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B41" s="19">
+        <f>B40+$F$26</f>
+        <v/>
+      </c>
+      <c r="C41" s="19">
+        <f>C40+E40*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D41" s="19">
+        <f>MAX(0.02,(D40+(F40-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E41" s="19">
+        <f>IF((D40+(F40-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E40*EXP(-$C$26*$F$26)*$E$26,E40*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F41" s="19">
+        <f>IF((D40+(F40-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F40-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F40-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B42" s="19">
+        <f>B41+$F$26</f>
+        <v/>
+      </c>
+      <c r="C42" s="19">
+        <f>C41+E41*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D42" s="19">
+        <f>MAX(0.02,(D41+(F41-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E42" s="19">
+        <f>IF((D41+(F41-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E41*EXP(-$C$26*$F$26)*$E$26,E41*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F42" s="19">
+        <f>IF((D41+(F41-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F41-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F41-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B43" s="19">
+        <f>B42+$F$26</f>
+        <v/>
+      </c>
+      <c r="C43" s="19">
+        <f>C42+E42*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D43" s="19">
+        <f>MAX(0.02,(D42+(F42-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E43" s="19">
+        <f>IF((D42+(F42-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E42*EXP(-$C$26*$F$26)*$E$26,E42*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F43" s="19">
+        <f>IF((D42+(F42-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F42-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F42-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B44" s="19">
+        <f>B43+$F$26</f>
+        <v/>
+      </c>
+      <c r="C44" s="19">
+        <f>C43+E43*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D44" s="19">
+        <f>MAX(0.02,(D43+(F43-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E44" s="19">
+        <f>IF((D43+(F43-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E43*EXP(-$C$26*$F$26)*$E$26,E43*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F44" s="19">
+        <f>IF((D43+(F43-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F43-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F43-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B45" s="19">
+        <f>B44+$F$26</f>
+        <v/>
+      </c>
+      <c r="C45" s="19">
+        <f>C44+E44*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D45" s="19">
+        <f>MAX(0.02,(D44+(F44-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E45" s="19">
+        <f>IF((D44+(F44-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E44*EXP(-$C$26*$F$26)*$E$26,E44*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F45" s="19">
+        <f>IF((D44+(F44-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F44-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F44-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B46" s="19">
+        <f>B45+$F$26</f>
+        <v/>
+      </c>
+      <c r="C46" s="19">
+        <f>C45+E45*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D46" s="19">
+        <f>MAX(0.02,(D45+(F45-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E46" s="19">
+        <f>IF((D45+(F45-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E45*EXP(-$C$26*$F$26)*$E$26,E45*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F46" s="19">
+        <f>IF((D45+(F45-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F45-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F45-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B47" s="19">
+        <f>B46+$F$26</f>
+        <v/>
+      </c>
+      <c r="C47" s="19">
+        <f>C46+E46*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D47" s="19">
+        <f>MAX(0.02,(D46+(F46-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E47" s="19">
+        <f>IF((D46+(F46-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E46*EXP(-$C$26*$F$26)*$E$26,E46*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F47" s="19">
+        <f>IF((D46+(F46-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F46-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F46-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B48" s="19">
+        <f>B47+$F$26</f>
+        <v/>
+      </c>
+      <c r="C48" s="19">
+        <f>C47+E47*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D48" s="19">
+        <f>MAX(0.02,(D47+(F47-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E48" s="19">
+        <f>IF((D47+(F47-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E47*EXP(-$C$26*$F$26)*$E$26,E47*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F48" s="19">
+        <f>IF((D47+(F47-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F47-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F47-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B49" s="19">
+        <f>B48+$F$26</f>
+        <v/>
+      </c>
+      <c r="C49" s="19">
+        <f>C48+E48*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D49" s="19">
+        <f>MAX(0.02,(D48+(F48-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E49" s="19">
+        <f>IF((D48+(F48-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E48*EXP(-$C$26*$F$26)*$E$26,E48*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F49" s="19">
+        <f>IF((D48+(F48-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F48-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F48-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B50" s="19">
+        <f>B49+$F$26</f>
+        <v/>
+      </c>
+      <c r="C50" s="19">
+        <f>C49+E49*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D50" s="19">
+        <f>MAX(0.02,(D49+(F49-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E50" s="19">
+        <f>IF((D49+(F49-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E49*EXP(-$C$26*$F$26)*$E$26,E49*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F50" s="19">
+        <f>IF((D49+(F49-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F49-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F49-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B51" s="19">
+        <f>B50+$F$26</f>
+        <v/>
+      </c>
+      <c r="C51" s="19">
+        <f>C50+E50*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D51" s="19">
+        <f>MAX(0.02,(D50+(F50-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E51" s="19">
+        <f>IF((D50+(F50-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E50*EXP(-$C$26*$F$26)*$E$26,E50*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F51" s="19">
+        <f>IF((D50+(F50-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F50-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F50-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B52" s="19">
+        <f>B51+$F$26</f>
+        <v/>
+      </c>
+      <c r="C52" s="19">
+        <f>C51+E51*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D52" s="19">
+        <f>MAX(0.02,(D51+(F51-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E52" s="19">
+        <f>IF((D51+(F51-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E51*EXP(-$C$26*$F$26)*$E$26,E51*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F52" s="19">
+        <f>IF((D51+(F51-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F51-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F51-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B53" s="19">
+        <f>B52+$F$26</f>
+        <v/>
+      </c>
+      <c r="C53" s="19">
+        <f>C52+E52*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D53" s="19">
+        <f>MAX(0.02,(D52+(F52-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E53" s="19">
+        <f>IF((D52+(F52-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E52*EXP(-$C$26*$F$26)*$E$26,E52*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F53" s="19">
+        <f>IF((D52+(F52-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F52-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F52-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B54" s="19">
+        <f>B53+$F$26</f>
+        <v/>
+      </c>
+      <c r="C54" s="19">
+        <f>C53+E53*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D54" s="19">
+        <f>MAX(0.02,(D53+(F53-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E54" s="19">
+        <f>IF((D53+(F53-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E53*EXP(-$C$26*$F$26)*$E$26,E53*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F54" s="19">
+        <f>IF((D53+(F53-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F53-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F53-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B55" s="19">
+        <f>B54+$F$26</f>
+        <v/>
+      </c>
+      <c r="C55" s="19">
+        <f>C54+E54*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D55" s="19">
+        <f>MAX(0.02,(D54+(F54-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E55" s="19">
+        <f>IF((D54+(F54-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E54*EXP(-$C$26*$F$26)*$E$26,E54*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F55" s="19">
+        <f>IF((D54+(F54-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F54-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F54-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B56" s="19">
+        <f>B55+$F$26</f>
+        <v/>
+      </c>
+      <c r="C56" s="19">
+        <f>C55+E55*EXP(-$C$26*$F$26)*$F$26</f>
+        <v/>
+      </c>
+      <c r="D56" s="19">
+        <f>MAX(0.02,(D55+(F55-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v/>
+      </c>
+      <c r="E56" s="19">
+        <f>IF((D55+(F55-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E55*EXP(-$C$26*$F$26)*$E$26,E55*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+      <c r="F56" s="19">
+        <f>IF((D55+(F55-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F55-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F55-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="80"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1881,7 +5315,7 @@
         </is>
       </c>
       <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="31">
+      <c r="Q5" s="32">
         <f>$H$5-$D$5</f>
         <v/>
       </c>
@@ -1891,7 +5325,7 @@
         </is>
       </c>
       <c r="T5" s="13" t="n"/>
-      <c r="U5" s="31">
+      <c r="U5" s="32">
         <f>24-($H$5-$D$5)</f>
         <v/>
       </c>
@@ -1969,36 +5403,36 @@
           <t>SENTRY</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>guard: inner gate and gate road (INNER GATE -&gt; GATE ROAD)</t>
         </is>
       </c>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="33" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="33" t="n"/>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="33" t="n"/>
-      <c r="J8" s="33" t="n"/>
-      <c r="K8" s="33" t="n"/>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="33" t="n"/>
-      <c r="N8" s="34" t="n"/>
-      <c r="O8" s="32" t="inlineStr">
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n"/>
+      <c r="F8" s="34" t="n"/>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
+      <c r="J8" s="34" t="n"/>
+      <c r="K8" s="34" t="n"/>
+      <c r="L8" s="34" t="n"/>
+      <c r="M8" s="34" t="n"/>
+      <c r="N8" s="35" t="n"/>
+      <c r="O8" s="33" t="inlineStr">
         <is>
           <t>guard: inner gate (INNER GATE)</t>
         </is>
       </c>
-      <c r="P8" s="33" t="n"/>
-      <c r="Q8" s="33" t="n"/>
-      <c r="R8" s="33" t="n"/>
-      <c r="S8" s="33" t="n"/>
-      <c r="T8" s="33" t="n"/>
-      <c r="U8" s="33" t="n"/>
-      <c r="V8" s="33" t="n"/>
-      <c r="W8" s="33" t="n"/>
-      <c r="X8" s="34" t="n"/>
+      <c r="P8" s="34" t="n"/>
+      <c r="Q8" s="34" t="n"/>
+      <c r="R8" s="34" t="n"/>
+      <c r="S8" s="34" t="n"/>
+      <c r="T8" s="34" t="n"/>
+      <c r="U8" s="34" t="n"/>
+      <c r="V8" s="34" t="n"/>
+      <c r="W8" s="34" t="n"/>
+      <c r="X8" s="35" t="n"/>
       <c r="Y8" s="15">
         <f>IF(LEFT(C8,FIND(":",C8)-1)="off duty","off",LEFT(C8,FIND(":",C8)-1))</f>
         <v/>
@@ -2017,36 +5451,36 @@
           <t>WATCH</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>guard: watchtower and east wood look-out (WATCHTOWER -&gt; EAST WOOD)</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="33" t="n"/>
-      <c r="I9" s="33" t="n"/>
-      <c r="J9" s="33" t="n"/>
-      <c r="K9" s="33" t="n"/>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="33" t="n"/>
-      <c r="N9" s="34" t="n"/>
-      <c r="O9" s="32" t="inlineStr">
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="34" t="n"/>
+      <c r="I9" s="34" t="n"/>
+      <c r="J9" s="34" t="n"/>
+      <c r="K9" s="34" t="n"/>
+      <c r="L9" s="34" t="n"/>
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="35" t="n"/>
+      <c r="O9" s="33" t="inlineStr">
         <is>
           <t>guard: sandbag guard post (SANDBAG POST)</t>
         </is>
       </c>
-      <c r="P9" s="33" t="n"/>
-      <c r="Q9" s="33" t="n"/>
-      <c r="R9" s="33" t="n"/>
-      <c r="S9" s="33" t="n"/>
-      <c r="T9" s="33" t="n"/>
-      <c r="U9" s="33" t="n"/>
-      <c r="V9" s="33" t="n"/>
-      <c r="W9" s="33" t="n"/>
-      <c r="X9" s="34" t="n"/>
+      <c r="P9" s="34" t="n"/>
+      <c r="Q9" s="34" t="n"/>
+      <c r="R9" s="34" t="n"/>
+      <c r="S9" s="34" t="n"/>
+      <c r="T9" s="34" t="n"/>
+      <c r="U9" s="34" t="n"/>
+      <c r="V9" s="34" t="n"/>
+      <c r="W9" s="34" t="n"/>
+      <c r="X9" s="35" t="n"/>
       <c r="Y9" s="15">
         <f>IF(LEFT(C9,FIND(":",C9)-1)="off duty","off",LEFT(C9,FIND(":",C9)-1))</f>
         <v/>
@@ -2065,36 +5499,36 @@
           <t>GUNNER</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>walk: patrol loop on the east apron</t>
         </is>
       </c>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="33" t="n"/>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="33" t="n"/>
-      <c r="K10" s="33" t="n"/>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="33" t="n"/>
-      <c r="N10" s="34" t="n"/>
-      <c r="O10" s="32" t="inlineStr">
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="34" t="n"/>
+      <c r="H10" s="34" t="n"/>
+      <c r="I10" s="34" t="n"/>
+      <c r="J10" s="34" t="n"/>
+      <c r="K10" s="34" t="n"/>
+      <c r="L10" s="34" t="n"/>
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="35" t="n"/>
+      <c r="O10" s="33" t="inlineStr">
         <is>
           <t>guard: machine-gun nest (MG NEST)</t>
         </is>
       </c>
-      <c r="P10" s="33" t="n"/>
-      <c r="Q10" s="33" t="n"/>
-      <c r="R10" s="33" t="n"/>
-      <c r="S10" s="33" t="n"/>
-      <c r="T10" s="33" t="n"/>
-      <c r="U10" s="33" t="n"/>
-      <c r="V10" s="33" t="n"/>
-      <c r="W10" s="33" t="n"/>
-      <c r="X10" s="34" t="n"/>
+      <c r="P10" s="34" t="n"/>
+      <c r="Q10" s="34" t="n"/>
+      <c r="R10" s="34" t="n"/>
+      <c r="S10" s="34" t="n"/>
+      <c r="T10" s="34" t="n"/>
+      <c r="U10" s="34" t="n"/>
+      <c r="V10" s="34" t="n"/>
+      <c r="W10" s="34" t="n"/>
+      <c r="X10" s="35" t="n"/>
       <c r="Y10" s="15">
         <f>IF(LEFT(C10,FIND(":",C10)-1)="off duty","off",LEFT(C10,FIND(":",C10)-1))</f>
         <v/>
@@ -2113,36 +5547,36 @@
           <t>MECHANIC</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>work: wrench at the parked tank and the helicopter (MBT-2 ENGINE DECK -&gt; HELICOPTER)</t>
         </is>
       </c>
-      <c r="D11" s="33" t="n"/>
-      <c r="E11" s="33" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="33" t="n"/>
-      <c r="H11" s="33" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="33" t="n"/>
-      <c r="K11" s="33" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="33" t="n"/>
-      <c r="N11" s="34" t="n"/>
-      <c r="O11" s="32" t="inlineStr">
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="34" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="35" t="n"/>
+      <c r="O11" s="33" t="inlineStr">
         <is>
           <t>off duty: bunk room (south bunk) (BUNK ROOM)</t>
         </is>
       </c>
-      <c r="P11" s="33" t="n"/>
-      <c r="Q11" s="33" t="n"/>
-      <c r="R11" s="33" t="n"/>
-      <c r="S11" s="33" t="n"/>
-      <c r="T11" s="33" t="n"/>
-      <c r="U11" s="33" t="n"/>
-      <c r="V11" s="33" t="n"/>
-      <c r="W11" s="33" t="n"/>
-      <c r="X11" s="34" t="n"/>
+      <c r="P11" s="34" t="n"/>
+      <c r="Q11" s="34" t="n"/>
+      <c r="R11" s="34" t="n"/>
+      <c r="S11" s="34" t="n"/>
+      <c r="T11" s="34" t="n"/>
+      <c r="U11" s="34" t="n"/>
+      <c r="V11" s="34" t="n"/>
+      <c r="W11" s="34" t="n"/>
+      <c r="X11" s="35" t="n"/>
       <c r="Y11" s="15">
         <f>IF(LEFT(C11,FIND(":",C11)-1)="off duty","off",LEFT(C11,FIND(":",C11)-1))</f>
         <v/>
@@ -2161,36 +5595,36 @@
           <t>LOGISTICS</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>work: carry crates from the depot to the ammunition bunker (FUEL DEPOT -&gt; AMMO BUNKER)</t>
         </is>
       </c>
-      <c r="D12" s="33" t="n"/>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="33" t="n"/>
-      <c r="H12" s="33" t="n"/>
-      <c r="I12" s="33" t="n"/>
-      <c r="J12" s="33" t="n"/>
-      <c r="K12" s="33" t="n"/>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="33" t="n"/>
-      <c r="N12" s="34" t="n"/>
-      <c r="O12" s="32" t="inlineStr">
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="34" t="n"/>
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="34" t="n"/>
+      <c r="I12" s="34" t="n"/>
+      <c r="J12" s="34" t="n"/>
+      <c r="K12" s="34" t="n"/>
+      <c r="L12" s="34" t="n"/>
+      <c r="M12" s="34" t="n"/>
+      <c r="N12" s="35" t="n"/>
+      <c r="O12" s="33" t="inlineStr">
         <is>
           <t>off duty: bunk room (mess table) (MESS BENCH)</t>
         </is>
       </c>
-      <c r="P12" s="33" t="n"/>
-      <c r="Q12" s="33" t="n"/>
-      <c r="R12" s="33" t="n"/>
-      <c r="S12" s="33" t="n"/>
-      <c r="T12" s="33" t="n"/>
-      <c r="U12" s="33" t="n"/>
-      <c r="V12" s="33" t="n"/>
-      <c r="W12" s="33" t="n"/>
-      <c r="X12" s="34" t="n"/>
+      <c r="P12" s="34" t="n"/>
+      <c r="Q12" s="34" t="n"/>
+      <c r="R12" s="34" t="n"/>
+      <c r="S12" s="34" t="n"/>
+      <c r="T12" s="34" t="n"/>
+      <c r="U12" s="34" t="n"/>
+      <c r="V12" s="34" t="n"/>
+      <c r="W12" s="34" t="n"/>
+      <c r="X12" s="35" t="n"/>
       <c r="Y12" s="15">
         <f>IF(LEFT(C12,FIND(":",C12)-1)="off duty","off",LEFT(C12,FIND(":",C12)-1))</f>
         <v/>
@@ -2209,36 +5643,36 @@
           <t>TECHNICIAN</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>work: inspect the radar and the AA gun (RADAR -&gt; AA GUN PIT)</t>
         </is>
       </c>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="33" t="n"/>
-      <c r="H13" s="33" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="33" t="n"/>
-      <c r="K13" s="33" t="n"/>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="33" t="n"/>
-      <c r="N13" s="34" t="n"/>
-      <c r="O13" s="32" t="inlineStr">
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="34" t="n"/>
+      <c r="H13" s="34" t="n"/>
+      <c r="I13" s="34" t="n"/>
+      <c r="J13" s="34" t="n"/>
+      <c r="K13" s="34" t="n"/>
+      <c r="L13" s="34" t="n"/>
+      <c r="M13" s="34" t="n"/>
+      <c r="N13" s="35" t="n"/>
+      <c r="O13" s="33" t="inlineStr">
         <is>
           <t>work: plotting table in the command room (COMMAND ROOM)</t>
         </is>
       </c>
-      <c r="P13" s="33" t="n"/>
-      <c r="Q13" s="33" t="n"/>
-      <c r="R13" s="33" t="n"/>
-      <c r="S13" s="33" t="n"/>
-      <c r="T13" s="33" t="n"/>
-      <c r="U13" s="33" t="n"/>
-      <c r="V13" s="33" t="n"/>
-      <c r="W13" s="33" t="n"/>
-      <c r="X13" s="34" t="n"/>
+      <c r="P13" s="34" t="n"/>
+      <c r="Q13" s="34" t="n"/>
+      <c r="R13" s="34" t="n"/>
+      <c r="S13" s="34" t="n"/>
+      <c r="T13" s="34" t="n"/>
+      <c r="U13" s="34" t="n"/>
+      <c r="V13" s="34" t="n"/>
+      <c r="W13" s="34" t="n"/>
+      <c r="X13" s="35" t="n"/>
       <c r="Y13" s="15">
         <f>IF(LEFT(C13,FIND(":",C13)-1)="off duty","off",LEFT(C13,FIND(":",C13)-1))</f>
         <v/>
@@ -2257,36 +5691,36 @@
           <t>PATROL</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>walk: patrol loop inside the compound</t>
         </is>
       </c>
-      <c r="D14" s="33" t="n"/>
-      <c r="E14" s="33" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="33" t="n"/>
-      <c r="H14" s="33" t="n"/>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="33" t="n"/>
-      <c r="K14" s="33" t="n"/>
-      <c r="L14" s="33" t="n"/>
-      <c r="M14" s="33" t="n"/>
-      <c r="N14" s="34" t="n"/>
-      <c r="O14" s="32" t="inlineStr">
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="34" t="n"/>
+      <c r="G14" s="34" t="n"/>
+      <c r="H14" s="34" t="n"/>
+      <c r="I14" s="34" t="n"/>
+      <c r="J14" s="34" t="n"/>
+      <c r="K14" s="34" t="n"/>
+      <c r="L14" s="34" t="n"/>
+      <c r="M14" s="34" t="n"/>
+      <c r="N14" s="35" t="n"/>
+      <c r="O14" s="33" t="inlineStr">
         <is>
           <t>guard: east guard tower (GUARD TOWER E)</t>
         </is>
       </c>
-      <c r="P14" s="33" t="n"/>
-      <c r="Q14" s="33" t="n"/>
-      <c r="R14" s="33" t="n"/>
-      <c r="S14" s="33" t="n"/>
-      <c r="T14" s="33" t="n"/>
-      <c r="U14" s="33" t="n"/>
-      <c r="V14" s="33" t="n"/>
-      <c r="W14" s="33" t="n"/>
-      <c r="X14" s="34" t="n"/>
+      <c r="P14" s="34" t="n"/>
+      <c r="Q14" s="34" t="n"/>
+      <c r="R14" s="34" t="n"/>
+      <c r="S14" s="34" t="n"/>
+      <c r="T14" s="34" t="n"/>
+      <c r="U14" s="34" t="n"/>
+      <c r="V14" s="34" t="n"/>
+      <c r="W14" s="34" t="n"/>
+      <c r="X14" s="35" t="n"/>
       <c r="Y14" s="15">
         <f>IF(LEFT(C14,FIND(":",C14)-1)="off duty","off",LEFT(C14,FIND(":",C14)-1))</f>
         <v/>
@@ -2305,36 +5739,36 @@
           <t>RUNNER</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>run: running loop on the south apron</t>
         </is>
       </c>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="33" t="n"/>
-      <c r="H15" s="33" t="n"/>
-      <c r="I15" s="33" t="n"/>
-      <c r="J15" s="33" t="n"/>
-      <c r="K15" s="33" t="n"/>
-      <c r="L15" s="33" t="n"/>
-      <c r="M15" s="33" t="n"/>
-      <c r="N15" s="34" t="n"/>
-      <c r="O15" s="32" t="inlineStr">
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="34" t="n"/>
+      <c r="J15" s="34" t="n"/>
+      <c r="K15" s="34" t="n"/>
+      <c r="L15" s="34" t="n"/>
+      <c r="M15" s="34" t="n"/>
+      <c r="N15" s="35" t="n"/>
+      <c r="O15" s="33" t="inlineStr">
         <is>
           <t>off duty: bunk room (north bunk) (BUNK ROOM)</t>
         </is>
       </c>
-      <c r="P15" s="33" t="n"/>
-      <c r="Q15" s="33" t="n"/>
-      <c r="R15" s="33" t="n"/>
-      <c r="S15" s="33" t="n"/>
-      <c r="T15" s="33" t="n"/>
-      <c r="U15" s="33" t="n"/>
-      <c r="V15" s="33" t="n"/>
-      <c r="W15" s="33" t="n"/>
-      <c r="X15" s="34" t="n"/>
+      <c r="P15" s="34" t="n"/>
+      <c r="Q15" s="34" t="n"/>
+      <c r="R15" s="34" t="n"/>
+      <c r="S15" s="34" t="n"/>
+      <c r="T15" s="34" t="n"/>
+      <c r="U15" s="34" t="n"/>
+      <c r="V15" s="34" t="n"/>
+      <c r="W15" s="34" t="n"/>
+      <c r="X15" s="35" t="n"/>
       <c r="Y15" s="15">
         <f>IF(LEFT(C15,FIND(":",C15)-1)="off duty","off",LEFT(C15,FIND(":",C15)-1))</f>
         <v/>
@@ -2362,76 +5796,76 @@
           <t>role</t>
         </is>
       </c>
-      <c r="C18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="35" t="n">
+      <c r="C18" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="35" t="n">
+      <c r="G18" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="35" t="n">
+      <c r="H18" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="I18" s="35" t="n">
+      <c r="I18" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="J18" s="35" t="n">
+      <c r="J18" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="K18" s="35" t="n">
+      <c r="K18" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="L18" s="35" t="n">
+      <c r="L18" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="M18" s="35" t="n">
+      <c r="M18" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="N18" s="35" t="n">
+      <c r="N18" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="O18" s="35" t="n">
+      <c r="O18" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="P18" s="35" t="n">
+      <c r="P18" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="Q18" s="35" t="n">
+      <c r="Q18" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="R18" s="35" t="n">
+      <c r="R18" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="S18" s="35" t="n">
+      <c r="S18" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="T18" s="35" t="n">
+      <c r="T18" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="U18" s="35" t="n">
+      <c r="U18" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="V18" s="35" t="n">
+      <c r="V18" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="W18" s="35" t="n">
+      <c r="W18" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="X18" s="35" t="n">
+      <c r="X18" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="Y18" s="35" t="n">
+      <c r="Y18" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="Z18" s="35" t="n">
+      <c r="Z18" s="36" t="n">
         <v>23</v>
       </c>
     </row>
@@ -2443,99 +5877,99 @@
         <f>B8</f>
         <v/>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="37">
         <f>IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="37">
         <f>IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="37">
         <f>IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="37">
         <f>IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="37">
         <f>IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="37">
         <f>IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="I19" s="36">
+      <c r="I19" s="37">
         <f>IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="J19" s="36">
+      <c r="J19" s="37">
         <f>IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="K19" s="36">
+      <c r="K19" s="37">
         <f>IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="L19" s="36">
+      <c r="L19" s="37">
         <f>IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="M19" s="36">
+      <c r="M19" s="37">
         <f>IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="N19" s="36">
+      <c r="N19" s="37">
         <f>IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="O19" s="36">
+      <c r="O19" s="37">
         <f>IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="P19" s="36">
+      <c r="P19" s="37">
         <f>IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="Q19" s="36">
+      <c r="Q19" s="37">
         <f>IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="R19" s="36">
+      <c r="R19" s="37">
         <f>IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="S19" s="36">
+      <c r="S19" s="37">
         <f>IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="T19" s="36">
+      <c r="T19" s="37">
         <f>IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="U19" s="36">
+      <c r="U19" s="37">
         <f>IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="V19" s="36">
+      <c r="V19" s="37">
         <f>IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="W19" s="36">
+      <c r="W19" s="37">
         <f>IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="X19" s="36">
+      <c r="X19" s="37">
         <f>IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="Y19" s="36">
+      <c r="Y19" s="37">
         <f>IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
-      <c r="Z19" s="36">
+      <c r="Z19" s="37">
         <f>IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v/>
       </c>
@@ -2548,99 +5982,99 @@
         <f>B9</f>
         <v/>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="37">
         <f>IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="37">
         <f>IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="37">
         <f>IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="37">
         <f>IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="37">
         <f>IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="37">
         <f>IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="37">
         <f>IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="J20" s="36">
+      <c r="J20" s="37">
         <f>IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="K20" s="36">
+      <c r="K20" s="37">
         <f>IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="L20" s="36">
+      <c r="L20" s="37">
         <f>IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="37">
         <f>IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="N20" s="36">
+      <c r="N20" s="37">
         <f>IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="O20" s="36">
+      <c r="O20" s="37">
         <f>IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="P20" s="36">
+      <c r="P20" s="37">
         <f>IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="Q20" s="36">
+      <c r="Q20" s="37">
         <f>IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="R20" s="36">
+      <c r="R20" s="37">
         <f>IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="S20" s="36">
+      <c r="S20" s="37">
         <f>IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="T20" s="36">
+      <c r="T20" s="37">
         <f>IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="U20" s="36">
+      <c r="U20" s="37">
         <f>IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="V20" s="36">
+      <c r="V20" s="37">
         <f>IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="W20" s="36">
+      <c r="W20" s="37">
         <f>IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="X20" s="36">
+      <c r="X20" s="37">
         <f>IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="Y20" s="36">
+      <c r="Y20" s="37">
         <f>IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
-      <c r="Z20" s="36">
+      <c r="Z20" s="37">
         <f>IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v/>
       </c>
@@ -2653,99 +6087,99 @@
         <f>B10</f>
         <v/>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="37">
         <f>IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="37">
         <f>IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="37">
         <f>IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="37">
         <f>IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="37">
         <f>IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="37">
         <f>IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="37">
         <f>IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="J21" s="36">
+      <c r="J21" s="37">
         <f>IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="K21" s="36">
+      <c r="K21" s="37">
         <f>IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="L21" s="36">
+      <c r="L21" s="37">
         <f>IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="M21" s="36">
+      <c r="M21" s="37">
         <f>IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="N21" s="36">
+      <c r="N21" s="37">
         <f>IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="O21" s="36">
+      <c r="O21" s="37">
         <f>IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="P21" s="36">
+      <c r="P21" s="37">
         <f>IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="Q21" s="36">
+      <c r="Q21" s="37">
         <f>IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="R21" s="36">
+      <c r="R21" s="37">
         <f>IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="S21" s="36">
+      <c r="S21" s="37">
         <f>IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="T21" s="36">
+      <c r="T21" s="37">
         <f>IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="U21" s="36">
+      <c r="U21" s="37">
         <f>IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="V21" s="36">
+      <c r="V21" s="37">
         <f>IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="W21" s="36">
+      <c r="W21" s="37">
         <f>IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="X21" s="36">
+      <c r="X21" s="37">
         <f>IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="Y21" s="36">
+      <c r="Y21" s="37">
         <f>IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
-      <c r="Z21" s="36">
+      <c r="Z21" s="37">
         <f>IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v/>
       </c>
@@ -2758,99 +6192,99 @@
         <f>B11</f>
         <v/>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="37">
         <f>IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="D22" s="36">
+      <c r="D22" s="37">
         <f>IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="37">
         <f>IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="37">
         <f>IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="37">
         <f>IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="37">
         <f>IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="37">
         <f>IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="J22" s="36">
+      <c r="J22" s="37">
         <f>IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="37">
         <f>IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="L22" s="36">
+      <c r="L22" s="37">
         <f>IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="37">
         <f>IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="N22" s="36">
+      <c r="N22" s="37">
         <f>IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="O22" s="36">
+      <c r="O22" s="37">
         <f>IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="P22" s="36">
+      <c r="P22" s="37">
         <f>IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="Q22" s="36">
+      <c r="Q22" s="37">
         <f>IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="R22" s="36">
+      <c r="R22" s="37">
         <f>IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="S22" s="36">
+      <c r="S22" s="37">
         <f>IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="T22" s="36">
+      <c r="T22" s="37">
         <f>IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="U22" s="36">
+      <c r="U22" s="37">
         <f>IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="V22" s="36">
+      <c r="V22" s="37">
         <f>IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="W22" s="36">
+      <c r="W22" s="37">
         <f>IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="X22" s="36">
+      <c r="X22" s="37">
         <f>IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="Y22" s="36">
+      <c r="Y22" s="37">
         <f>IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
-      <c r="Z22" s="36">
+      <c r="Z22" s="37">
         <f>IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v/>
       </c>
@@ -2863,99 +6297,99 @@
         <f>B12</f>
         <v/>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="37">
         <f>IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="D23" s="36">
+      <c r="D23" s="37">
         <f>IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="37">
         <f>IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="37">
         <f>IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="37">
         <f>IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="37">
         <f>IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="37">
         <f>IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="J23" s="36">
+      <c r="J23" s="37">
         <f>IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="K23" s="36">
+      <c r="K23" s="37">
         <f>IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="L23" s="36">
+      <c r="L23" s="37">
         <f>IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="M23" s="36">
+      <c r="M23" s="37">
         <f>IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="N23" s="36">
+      <c r="N23" s="37">
         <f>IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="O23" s="36">
+      <c r="O23" s="37">
         <f>IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="P23" s="36">
+      <c r="P23" s="37">
         <f>IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="Q23" s="36">
+      <c r="Q23" s="37">
         <f>IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="R23" s="36">
+      <c r="R23" s="37">
         <f>IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="S23" s="36">
+      <c r="S23" s="37">
         <f>IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="T23" s="36">
+      <c r="T23" s="37">
         <f>IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="U23" s="36">
+      <c r="U23" s="37">
         <f>IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="V23" s="36">
+      <c r="V23" s="37">
         <f>IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="W23" s="36">
+      <c r="W23" s="37">
         <f>IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="X23" s="36">
+      <c r="X23" s="37">
         <f>IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="Y23" s="36">
+      <c r="Y23" s="37">
         <f>IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
-      <c r="Z23" s="36">
+      <c r="Z23" s="37">
         <f>IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v/>
       </c>
@@ -2968,99 +6402,99 @@
         <f>B13</f>
         <v/>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="37">
         <f>IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="37">
         <f>IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="37">
         <f>IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="F24" s="36">
+      <c r="F24" s="37">
         <f>IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="37">
         <f>IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="37">
         <f>IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="I24" s="36">
+      <c r="I24" s="37">
         <f>IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="J24" s="36">
+      <c r="J24" s="37">
         <f>IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="37">
         <f>IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="L24" s="36">
+      <c r="L24" s="37">
         <f>IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="M24" s="36">
+      <c r="M24" s="37">
         <f>IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="N24" s="36">
+      <c r="N24" s="37">
         <f>IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="O24" s="36">
+      <c r="O24" s="37">
         <f>IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="P24" s="36">
+      <c r="P24" s="37">
         <f>IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="Q24" s="36">
+      <c r="Q24" s="37">
         <f>IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="R24" s="36">
+      <c r="R24" s="37">
         <f>IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="S24" s="36">
+      <c r="S24" s="37">
         <f>IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="T24" s="36">
+      <c r="T24" s="37">
         <f>IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="U24" s="36">
+      <c r="U24" s="37">
         <f>IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="V24" s="36">
+      <c r="V24" s="37">
         <f>IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="W24" s="36">
+      <c r="W24" s="37">
         <f>IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="X24" s="36">
+      <c r="X24" s="37">
         <f>IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="Y24" s="36">
+      <c r="Y24" s="37">
         <f>IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
-      <c r="Z24" s="36">
+      <c r="Z24" s="37">
         <f>IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v/>
       </c>
@@ -3073,99 +6507,99 @@
         <f>B14</f>
         <v/>
       </c>
-      <c r="C25" s="36">
+      <c r="C25" s="37">
         <f>IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="D25" s="36">
+      <c r="D25" s="37">
         <f>IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="E25" s="36">
+      <c r="E25" s="37">
         <f>IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="37">
         <f>IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="37">
         <f>IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="37">
         <f>IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="I25" s="36">
+      <c r="I25" s="37">
         <f>IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="J25" s="36">
+      <c r="J25" s="37">
         <f>IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="K25" s="36">
+      <c r="K25" s="37">
         <f>IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="L25" s="36">
+      <c r="L25" s="37">
         <f>IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="M25" s="36">
+      <c r="M25" s="37">
         <f>IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="N25" s="36">
+      <c r="N25" s="37">
         <f>IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="O25" s="36">
+      <c r="O25" s="37">
         <f>IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="P25" s="36">
+      <c r="P25" s="37">
         <f>IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="Q25" s="36">
+      <c r="Q25" s="37">
         <f>IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="R25" s="36">
+      <c r="R25" s="37">
         <f>IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="S25" s="36">
+      <c r="S25" s="37">
         <f>IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="T25" s="36">
+      <c r="T25" s="37">
         <f>IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="U25" s="36">
+      <c r="U25" s="37">
         <f>IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="V25" s="36">
+      <c r="V25" s="37">
         <f>IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="W25" s="36">
+      <c r="W25" s="37">
         <f>IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="X25" s="36">
+      <c r="X25" s="37">
         <f>IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="Y25" s="36">
+      <c r="Y25" s="37">
         <f>IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
-      <c r="Z25" s="36">
+      <c r="Z25" s="37">
         <f>IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v/>
       </c>
@@ -3178,99 +6612,99 @@
         <f>B15</f>
         <v/>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="37">
         <f>IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="37">
         <f>IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="37">
         <f>IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="37">
         <f>IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="37">
         <f>IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="H26" s="36">
+      <c r="H26" s="37">
         <f>IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="I26" s="36">
+      <c r="I26" s="37">
         <f>IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="J26" s="36">
+      <c r="J26" s="37">
         <f>IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="K26" s="36">
+      <c r="K26" s="37">
         <f>IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="L26" s="36">
+      <c r="L26" s="37">
         <f>IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="M26" s="36">
+      <c r="M26" s="37">
         <f>IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="N26" s="36">
+      <c r="N26" s="37">
         <f>IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="O26" s="36">
+      <c r="O26" s="37">
         <f>IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="P26" s="36">
+      <c r="P26" s="37">
         <f>IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="Q26" s="36">
+      <c r="Q26" s="37">
         <f>IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="R26" s="36">
+      <c r="R26" s="37">
         <f>IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="S26" s="36">
+      <c r="S26" s="37">
         <f>IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="T26" s="36">
+      <c r="T26" s="37">
         <f>IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="U26" s="36">
+      <c r="U26" s="37">
         <f>IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="V26" s="36">
+      <c r="V26" s="37">
         <f>IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="W26" s="36">
+      <c r="W26" s="37">
         <f>IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="X26" s="36">
+      <c r="X26" s="37">
         <f>IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="Y26" s="36">
+      <c r="Y26" s="37">
         <f>IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
-      <c r="Z26" s="36">
+      <c r="Z26" s="37">
         <f>IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v/>
       </c>
@@ -3386,99 +6820,99 @@
         </is>
       </c>
       <c r="B28" s="13" t="n"/>
-      <c r="C28" s="37">
+      <c r="C28" s="38">
         <f>IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="D28" s="37">
+      <c r="D28" s="38">
         <f>IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="E28" s="37">
+      <c r="E28" s="38">
         <f>IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="F28" s="37">
+      <c r="F28" s="38">
         <f>IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="38">
         <f>IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="H28" s="37">
+      <c r="H28" s="38">
         <f>IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="38">
         <f>IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="J28" s="37">
+      <c r="J28" s="38">
         <f>IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="K28" s="37">
+      <c r="K28" s="38">
         <f>IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="L28" s="37">
+      <c r="L28" s="38">
         <f>IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="M28" s="37">
+      <c r="M28" s="38">
         <f>IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="N28" s="37">
+      <c r="N28" s="38">
         <f>IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="O28" s="37">
+      <c r="O28" s="38">
         <f>IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="P28" s="37">
+      <c r="P28" s="38">
         <f>IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="Q28" s="37">
+      <c r="Q28" s="38">
         <f>IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="R28" s="37">
+      <c r="R28" s="38">
         <f>IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="S28" s="37">
+      <c r="S28" s="38">
         <f>IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="T28" s="37">
+      <c r="T28" s="38">
         <f>IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="U28" s="37">
+      <c r="U28" s="38">
         <f>IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="V28" s="37">
+      <c r="V28" s="38">
         <f>IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="W28" s="37">
+      <c r="W28" s="38">
         <f>IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="X28" s="37">
+      <c r="X28" s="38">
         <f>IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="Y28" s="37">
+      <c r="Y28" s="38">
         <f>IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
-      <c r="Z28" s="37">
+      <c r="Z28" s="38">
         <f>IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v/>
       </c>
@@ -3544,42 +6978,42 @@
         </is>
       </c>
       <c r="B33" s="13" t="n"/>
-      <c r="C33" s="38">
+      <c r="C33" s="39">
         <f>1+2.5*C32</f>
         <v/>
       </c>
       <c r="D33" s="13" t="n"/>
-      <c r="E33" s="38">
+      <c r="E33" s="39">
         <f>1+2.5*E32</f>
         <v/>
       </c>
       <c r="F33" s="13" t="n"/>
-      <c r="G33" s="38">
+      <c r="G33" s="39">
         <f>1+2.5*G32</f>
         <v/>
       </c>
       <c r="H33" s="13" t="n"/>
-      <c r="I33" s="38">
+      <c r="I33" s="39">
         <f>1+2.5*I32</f>
         <v/>
       </c>
       <c r="J33" s="13" t="n"/>
-      <c r="K33" s="38">
+      <c r="K33" s="39">
         <f>1+2.5*K32</f>
         <v/>
       </c>
       <c r="L33" s="13" t="n"/>
-      <c r="M33" s="38">
+      <c r="M33" s="39">
         <f>1+2.5*M32</f>
         <v/>
       </c>
       <c r="N33" s="13" t="n"/>
-      <c r="O33" s="38">
+      <c r="O33" s="39">
         <f>1+2.5*O32</f>
         <v/>
       </c>
       <c r="P33" s="13" t="n"/>
-      <c r="Q33" s="38">
+      <c r="Q33" s="39">
         <f>1+2.5*Q32</f>
         <v/>
       </c>
@@ -3671,7 +7105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/report/workbooks/cg_workbook.xlsx
+++ b/report/workbooks/cg_workbook.xlsx
@@ -1183,7 +1183,7 @@
         <v/>
       </c>
       <c r="P7" s="8" t="n">
-        <v>2443</v>
+        <v>2452</v>
       </c>
       <c r="Q7" s="7">
         <f>M7*P7</f>
@@ -1252,7 +1252,7 @@
         <v/>
       </c>
       <c r="P8" s="8" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="Q8" s="7">
         <f>M8*P8</f>
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="P10" s="8" t="n">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="Q10" s="7">
         <f>M10*P10</f>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -11036,7 +11036,7 @@
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>1</v>
@@ -11045,7 +11045,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J10" s="7" t="n"/>
       <c r="K10" s="7" t="n"/>
@@ -11058,7 +11058,7 @@
         <v/>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="R10" s="15">
         <f>IF(P10=Q10,"OK","DIFF")</f>
@@ -12736,7 +12736,7 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>2467</v>
+        <v>2476</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>6</v>
@@ -12748,7 +12748,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>10</v>
@@ -12757,7 +12757,7 @@
         <v>364</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="J39" s="8" t="n">
         <v>3</v>
@@ -12782,7 +12782,7 @@
         <v/>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>5476</v>
+        <v>5489</v>
       </c>
     </row>
     <row r="40">
@@ -23846,10 +23846,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="F20" s="7">
         <f>IF(ISNUMBER(D20),C20*D20,E20)</f>
@@ -23857,7 +23857,7 @@
       </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="8" t="n">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>1</v>
@@ -23865,7 +23865,7 @@
       <c r="J20" s="7" t="n"/>
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>1</v>
@@ -23874,7 +23874,7 @@
         <v>9</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P20" s="7" t="n"/>
       <c r="Q20" s="7" t="n"/>
@@ -26515,7 +26515,7 @@
         </is>
       </c>
       <c r="E70" s="8" t="n">
-        <v>5476</v>
+        <v>5489</v>
       </c>
       <c r="F70" s="15">
         <f>IF(E69=E70,"OK","DIFF")</f>
@@ -32913,7 +32913,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: scene/DayCycle (solar model, transmittance, 3.2 smoothstep(-1, 10, e), ambient mixLog); export 'lights'; ShaderSources.cpp brdf(); BNK-171 'Roof slab A'.</t>
+          <t>Source: scene/DayCycle (solar model, transmittance, 3.2 smoothstep(-1, 10, e), ambient mixLog); export 'lights'; ShaderSources.cpp brdf(); the command bunker's part 'Roof slab A'.</t>
         </is>
       </c>
     </row>
@@ -33510,7 +33510,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>roof albedo kd (BNK-171 colour)</t>
+          <t>roof albedo kd (Roof slab A colour)</t>
         </is>
       </c>
       <c r="I19" s="16" t="n">

--- a/report/workbooks/cg_workbook.xlsx
+++ b/report/workbooks/cg_workbook.xlsx
@@ -1183,7 +1183,7 @@
         <v/>
       </c>
       <c r="P7" s="8" t="n">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="Q7" s="7">
         <f>M7*P7</f>
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="P10" s="8" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="Q10" s="7">
         <f>M10*P10</f>
@@ -1891,7 +1891,7 @@
         <v/>
       </c>
       <c r="P17" s="8" t="n">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="Q17" s="7">
         <f>M17*P17</f>
@@ -10881,7 +10881,9 @@
           <t>Backdrop</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
+      <c r="B8" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
@@ -10891,7 +10893,7 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" s="7" t="n"/>
       <c r="K8" s="8" t="n">
@@ -10906,7 +10908,7 @@
         <v/>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="R8" s="15">
         <f>IF(P8=Q8,"OK","DIFF")</f>
@@ -12055,7 +12057,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
@@ -12065,7 +12067,7 @@
       </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="8" t="n">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="I25" s="8" t="n">
         <v>90</v>
@@ -12083,7 +12085,7 @@
         <v/>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="R25" s="15">
         <f>IF(P25=Q25,"OK","DIFF")</f>
@@ -12736,7 +12738,7 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>6</v>
@@ -12754,10 +12756,10 @@
         <v>10</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="J39" s="8" t="n">
         <v>3</v>
@@ -12782,7 +12784,7 @@
         <v/>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>5489</v>
+        <v>5474</v>
       </c>
     </row>
     <row r="40">
@@ -24937,11 +24939,11 @@
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>48..60</t>
+          <t>42..56</t>
         </is>
       </c>
       <c r="E40" s="8" t="n">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F40" s="7">
         <f>IF(ISNUMBER(D40),C40*D40,E40)</f>
@@ -24949,7 +24951,7 @@
       </c>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="8" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I40" s="7" t="n"/>
       <c r="J40" s="7" t="n"/>
@@ -24957,7 +24959,7 @@
       <c r="L40" s="7" t="n"/>
       <c r="M40" s="7" t="n"/>
       <c r="N40" s="8" t="n">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="O40" s="7" t="n"/>
       <c r="P40" s="7" t="n"/>
@@ -26135,29 +26137,29 @@
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D63" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63" s="7">
         <f>IF(ISNUMBER(D63),C63*D63,E63)</f>
         <v/>
       </c>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="n"/>
+      <c r="H63" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="I63" s="7" t="n"/>
       <c r="J63" s="7" t="n"/>
       <c r="K63" s="7" t="n"/>
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n"/>
-      <c r="O63" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="O63" s="7" t="n"/>
       <c r="P63" s="7" t="n"/>
       <c r="Q63" s="7" t="n"/>
       <c r="R63" s="7" t="n"/>
@@ -26515,7 +26517,7 @@
         </is>
       </c>
       <c r="E70" s="8" t="n">
-        <v>5489</v>
+        <v>5474</v>
       </c>
       <c r="F70" s="15">
         <f>IF(E69=E70,"OK","DIFF")</f>
